--- a/marketer_forms/007_internet_usage_survey_template--marketer_forms.xlsx
+++ b/marketer_forms/007_internet_usage_survey_template--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mobile',_'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mobile', 'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'desktop',_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Desktop', 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'laptop',_'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Laptop', 'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'several_times_a_week',_'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Several times a week', 'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'occasionally',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Occasionally', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'rarely',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Rarely', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'never',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Never', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'social_media', 'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'online_shopping',_'label':_'online_shopping'}</t>
+          <t>online_shopping</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'online_shopping', 'label': 'Online shopping'}</t>
+          <t>Online shopping</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'streaming_media',_'label':_'streaming_media'}</t>
+          <t>streaming_media</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'streaming_media', 'label': 'Streaming media'}</t>
+          <t>Streaming media</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'18-24',_'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '18-24', 'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'25-34',_'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '25-34', 'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'35-44',_'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '35-44', 'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'45-54',_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': '45-54', 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'55+',_'label':_'55+'}</t>
+          <t>55+</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': '55+', 'label': '55+'}</t>
+          <t>55+</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'text',_'label':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'text', 'label': 'Text message'}</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree',_'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'disagree', 'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'disagree',_'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'disagree', 'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
